--- a/output/pdf_financials_xlsx/VG.xlsx
+++ b/output/pdf_financials_xlsx/VG.xlsx
@@ -5982,25 +5982,25 @@
         <v>0.032806</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.321397</v>
+        <v>0.032806</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.270101</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.111759</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.104517</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.104517</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.104517</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.104517</v>
       </c>
       <c r="K92" s="3" t="n">
         <v>0</v>
@@ -14586,7 +14586,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -15071,7 +15075,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -15374,7 +15382,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -15982,7 +15994,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -16899,7 +16915,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -18228,7 +18248,11 @@
           <t>Reserves (Note 13) 270,101</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/VG.xlsx
+++ b/output/pdf_financials_xlsx/VG.xlsx
@@ -1037,13 +1037,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.00629</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.006869</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.001485</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1055,7 +1055,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.001528</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -2025,13 +2025,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.175391</v>
+        <v>-0.181681</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.161493</v>
+        <v>-0.168362</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.769007</v>
+        <v>-0.770492</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-2.460062</v>
@@ -2043,7 +2043,7 @@
         <v>-0.174708</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.8095</v>
+        <v>-0.811028</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.116095</v>
@@ -2141,13 +2141,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.175391</v>
+        <v>-0.181681</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.161493</v>
+        <v>-0.168362</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.769007</v>
+        <v>-0.770492</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-2.460062</v>
@@ -2159,7 +2159,7 @@
         <v>-0.174708</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.8095</v>
+        <v>-0.811028</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.116095</v>
@@ -2440,55 +2440,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.681582</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.435972</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.435972</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.433566</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.317356</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.247954</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.477841</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.416759</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.472746</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.155116</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.082675</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.162739</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>8.22442</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>5.595923</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>3.161749</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.837745</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>1.166437</v>
       </c>
     </row>
     <row r="35">
@@ -2556,55 +2556,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.681582</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.435972</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.435972</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.433566</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.317356</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.247954</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.477841</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.416759</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.472746</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.155116</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.082675</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.162739</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>8.22442</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>5.595923</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>3.161749</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.837745</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>1.166437</v>
       </c>
     </row>
     <row r="37">
@@ -3252,55 +3252,55 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.681582</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.635972</v>
+        <v>0.2</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.648878</v>
+        <v>0.212906</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.485944</v>
+        <v>0.052378</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.338435</v>
+        <v>0.021079</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.250481</v>
+        <v>0.002527</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.479174</v>
+        <v>0.001333</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.418516</v>
+        <v>0.001757</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.472746</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.221809</v>
+        <v>0.066693</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.08779000000000001</v>
+        <v>0.005115</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.165891</v>
+        <v>0.003152</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>8.278171</v>
+        <v>0.053751</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>5.624187</v>
+        <v>0.028264</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>3.181209</v>
+        <v>0.01946</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.85218</v>
+        <v>0.014435</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>1.217878</v>
+        <v>0.051441</v>
       </c>
     </row>
     <row r="49">
@@ -8665,7 +8665,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -17020,7 +17020,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -45026,7 +45026,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E369" s="5" t="n">

--- a/output/pdf_financials_xlsx/VG.xlsx
+++ b/output/pdf_financials_xlsx/VG.xlsx
@@ -4429,10 +4429,10 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="G67" s="3" t="n">
         <v>0</v>
@@ -6853,10 +6853,10 @@
         <v>0</v>
       </c>
       <c r="P107" s="3" t="n">
-        <v>0</v>
+        <v>0.042048</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>0</v>
+        <v>0.177034</v>
       </c>
       <c r="R107" s="3" t="n">
         <v>0</v>
@@ -6994,10 +6994,10 @@
         <v>0</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.000654</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.000216</v>
       </c>
       <c r="G110" s="3" t="n">
         <v>0</v>
@@ -7046,10 +7046,10 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002472</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.004612</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -7079,10 +7079,10 @@
         <v>0</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.195605</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.040303</v>
       </c>
       <c r="P111" s="3" t="n">
         <v>-0.002438</v>
@@ -8414,10 +8414,10 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002472</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.004612</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -8447,10 +8447,10 @@
         <v>0</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.195605</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.040303</v>
       </c>
       <c r="P134" s="3" t="n">
         <v>-0.002438</v>
@@ -8472,10 +8472,10 @@
         <v>-0.138376</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.165571</v>
+        <v>-0.168043</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.529635</v>
+        <v>-0.534247</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>-0.412503</v>
@@ -8505,10 +8505,10 @@
         <v>-0.290031</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-3.646568</v>
+        <v>-3.842173</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>-2.611583</v>
+        <v>-2.651886</v>
       </c>
       <c r="P135" s="3" t="n">
         <v>-2.229301</v>
@@ -20240,7 +20240,11 @@
           <t>Share-based payments expense</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -22348,7 +22352,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
@@ -32635,7 +32643,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -34857,7 +34869,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E266" t="inlineStr">
         <is>
           <t>-</t>
